--- a/data/raw/unemployment_rate.xlsx
+++ b/data/raw/unemployment_rate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/final_year_project/Unemployment-Analysis-and-Prediction-in-India-and-Pakistan/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2E0407-7E8E-0F43-97D8-DF6547F6C082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07F6070-F591-0642-8908-77D638A34820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4620" yWindow="3620" windowWidth="27640" windowHeight="16940" xr2:uid="{86C56294-0BB9-A546-8427-0088CA01ADD6}"/>
   </bookViews>
